--- a/figures/Fig3_mse_subteam_timeline.xlsx
+++ b/figures/Fig3_mse_subteam_timeline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/grants/dcrab_multistressor/figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E56DF9-6594-1842-BB3D-A6CD071066C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0571A9DB-4D7D-7141-8F0C-601532457DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13900" yWindow="1040" windowWidth="40620" windowHeight="21180" xr2:uid="{B774C1BA-0B64-334B-992A-B41393F1F4E3}"/>
+    <workbookView xWindow="6080" yWindow="4340" windowWidth="35840" windowHeight="20200" xr2:uid="{B774C1BA-0B64-334B-992A-B41393F1F4E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -450,36 +450,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -540,6 +510,36 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -868,545 +868,545 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:51" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="58" t="s">
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="60"/>
-      <c r="AA2" s="58" t="s">
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="60"/>
-      <c r="AM2" s="61" t="s">
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="49"/>
+      <c r="AG2" s="49"/>
+      <c r="AH2" s="49"/>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="49"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="AN2" s="62"/>
-      <c r="AO2" s="62"/>
-      <c r="AP2" s="62"/>
-      <c r="AQ2" s="62"/>
-      <c r="AR2" s="62"/>
-      <c r="AS2" s="62"/>
-      <c r="AT2" s="62"/>
-      <c r="AU2" s="62"/>
-      <c r="AV2" s="62"/>
-      <c r="AW2" s="62"/>
-      <c r="AX2" s="63"/>
+      <c r="AN2" s="52"/>
+      <c r="AO2" s="52"/>
+      <c r="AP2" s="52"/>
+      <c r="AQ2" s="52"/>
+      <c r="AR2" s="52"/>
+      <c r="AS2" s="52"/>
+      <c r="AT2" s="52"/>
+      <c r="AU2" s="52"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="53"/>
     </row>
     <row r="3" spans="2:51" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="31"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="29"/>
-      <c r="AC3" s="29"/>
-      <c r="AD3" s="29"/>
-      <c r="AE3" s="29"/>
-      <c r="AF3" s="29"/>
-      <c r="AG3" s="29"/>
-      <c r="AH3" s="29"/>
-      <c r="AI3" s="29"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="31"/>
-      <c r="AM3" s="32"/>
-      <c r="AN3" s="33"/>
-      <c r="AO3" s="33"/>
-      <c r="AP3" s="33"/>
-      <c r="AQ3" s="33"/>
-      <c r="AR3" s="33"/>
-      <c r="AS3" s="33"/>
-      <c r="AT3" s="33"/>
-      <c r="AU3" s="33"/>
-      <c r="AV3" s="33"/>
-      <c r="AW3" s="33"/>
-      <c r="AX3" s="34"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="20"/>
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="19"/>
+      <c r="AF3" s="19"/>
+      <c r="AG3" s="19"/>
+      <c r="AH3" s="19"/>
+      <c r="AI3" s="19"/>
+      <c r="AJ3" s="19"/>
+      <c r="AK3" s="19"/>
+      <c r="AL3" s="21"/>
+      <c r="AM3" s="22"/>
+      <c r="AN3" s="23"/>
+      <c r="AO3" s="23"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="23"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="23"/>
+      <c r="AT3" s="23"/>
+      <c r="AU3" s="23"/>
+      <c r="AV3" s="23"/>
+      <c r="AW3" s="23"/>
+      <c r="AX3" s="24"/>
     </row>
     <row r="4" spans="2:51" x14ac:dyDescent="0.2">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="45"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="29"/>
-      <c r="AI4" s="29"/>
-      <c r="AJ4" s="29"/>
-      <c r="AK4" s="29"/>
-      <c r="AL4" s="31"/>
-      <c r="AM4" s="32"/>
-      <c r="AN4" s="33"/>
-      <c r="AO4" s="33"/>
-      <c r="AP4" s="33"/>
-      <c r="AQ4" s="33"/>
-      <c r="AR4" s="33"/>
-      <c r="AS4" s="33"/>
-      <c r="AT4" s="33"/>
-      <c r="AU4" s="33"/>
-      <c r="AV4" s="33"/>
-      <c r="AW4" s="33"/>
-      <c r="AX4" s="34"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="19"/>
+      <c r="AC4" s="19"/>
+      <c r="AD4" s="19"/>
+      <c r="AE4" s="19"/>
+      <c r="AF4" s="19"/>
+      <c r="AG4" s="19"/>
+      <c r="AH4" s="19"/>
+      <c r="AI4" s="19"/>
+      <c r="AJ4" s="19"/>
+      <c r="AK4" s="19"/>
+      <c r="AL4" s="21"/>
+      <c r="AM4" s="22"/>
+      <c r="AN4" s="23"/>
+      <c r="AO4" s="23"/>
+      <c r="AP4" s="23"/>
+      <c r="AQ4" s="23"/>
+      <c r="AR4" s="23"/>
+      <c r="AS4" s="23"/>
+      <c r="AT4" s="23"/>
+      <c r="AU4" s="23"/>
+      <c r="AV4" s="23"/>
+      <c r="AW4" s="23"/>
+      <c r="AX4" s="24"/>
     </row>
     <row r="5" spans="2:51" x14ac:dyDescent="0.2">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40">
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30">
         <v>1</v>
       </c>
-      <c r="N5" s="41"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="40">
+      <c r="N5" s="31"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="19"/>
+      <c r="V5" s="19"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30">
         <v>2</v>
       </c>
-      <c r="Z5" s="41"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="29"/>
-      <c r="AI5" s="29"/>
-      <c r="AJ5" s="40"/>
-      <c r="AK5" s="40">
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="19"/>
+      <c r="AC5" s="19"/>
+      <c r="AD5" s="19"/>
+      <c r="AE5" s="19"/>
+      <c r="AF5" s="19"/>
+      <c r="AG5" s="19"/>
+      <c r="AH5" s="19"/>
+      <c r="AI5" s="19"/>
+      <c r="AJ5" s="30"/>
+      <c r="AK5" s="30">
         <v>3</v>
       </c>
-      <c r="AL5" s="41"/>
-      <c r="AM5" s="32"/>
-      <c r="AN5" s="33"/>
-      <c r="AO5" s="33"/>
-      <c r="AP5" s="40"/>
-      <c r="AQ5" s="40">
+      <c r="AL5" s="31"/>
+      <c r="AM5" s="22"/>
+      <c r="AN5" s="23"/>
+      <c r="AO5" s="23"/>
+      <c r="AP5" s="30"/>
+      <c r="AQ5" s="30">
         <v>4</v>
       </c>
-      <c r="AR5" s="56"/>
-      <c r="AU5" s="33"/>
-      <c r="AV5" s="33"/>
-      <c r="AW5" s="33"/>
-      <c r="AX5" s="34"/>
+      <c r="AR5" s="46"/>
+      <c r="AU5" s="23"/>
+      <c r="AV5" s="23"/>
+      <c r="AW5" s="23"/>
+      <c r="AX5" s="24"/>
     </row>
     <row r="6" spans="2:51" x14ac:dyDescent="0.2">
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="31"/>
-      <c r="AA6" s="47"/>
-      <c r="AB6" s="48"/>
-      <c r="AC6" s="48"/>
-      <c r="AD6" s="48"/>
-      <c r="AE6" s="48"/>
-      <c r="AF6" s="48"/>
-      <c r="AG6" s="48"/>
-      <c r="AH6" s="48"/>
-      <c r="AI6" s="48"/>
-      <c r="AJ6" s="48"/>
-      <c r="AK6" s="48"/>
-      <c r="AL6" s="49"/>
-      <c r="AM6" s="32"/>
-      <c r="AN6" s="33"/>
-      <c r="AO6" s="33"/>
-      <c r="AP6" s="33"/>
-      <c r="AQ6" s="33"/>
-      <c r="AR6" s="33"/>
-      <c r="AS6" s="33"/>
-      <c r="AT6" s="33"/>
-      <c r="AU6" s="33"/>
-      <c r="AV6" s="33"/>
-      <c r="AW6" s="33"/>
-      <c r="AX6" s="34"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="21"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="38"/>
+      <c r="AC6" s="38"/>
+      <c r="AD6" s="38"/>
+      <c r="AE6" s="38"/>
+      <c r="AF6" s="38"/>
+      <c r="AG6" s="38"/>
+      <c r="AH6" s="38"/>
+      <c r="AI6" s="38"/>
+      <c r="AJ6" s="38"/>
+      <c r="AK6" s="38"/>
+      <c r="AL6" s="39"/>
+      <c r="AM6" s="22"/>
+      <c r="AN6" s="23"/>
+      <c r="AO6" s="23"/>
+      <c r="AP6" s="23"/>
+      <c r="AQ6" s="23"/>
+      <c r="AR6" s="23"/>
+      <c r="AS6" s="23"/>
+      <c r="AT6" s="23"/>
+      <c r="AU6" s="23"/>
+      <c r="AV6" s="23"/>
+      <c r="AW6" s="23"/>
+      <c r="AX6" s="24"/>
     </row>
     <row r="7" spans="2:51" x14ac:dyDescent="0.2">
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="35"/>
-      <c r="AC7" s="35"/>
-      <c r="AD7" s="38"/>
-      <c r="AE7" s="38"/>
-      <c r="AF7" s="38"/>
-      <c r="AG7" s="38"/>
-      <c r="AH7" s="38"/>
-      <c r="AI7" s="38"/>
-      <c r="AJ7" s="38"/>
-      <c r="AK7" s="38"/>
-      <c r="AL7" s="36"/>
-      <c r="AM7" s="50"/>
-      <c r="AN7" s="51"/>
-      <c r="AO7" s="51"/>
-      <c r="AP7" s="51"/>
-      <c r="AQ7" s="51"/>
-      <c r="AR7" s="51"/>
-      <c r="AS7" s="33"/>
-      <c r="AT7" s="33"/>
-      <c r="AU7" s="33"/>
-      <c r="AV7" s="33"/>
-      <c r="AW7" s="33"/>
-      <c r="AX7" s="34"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="28"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="28"/>
+      <c r="Z7" s="26"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="28"/>
+      <c r="AF7" s="28"/>
+      <c r="AG7" s="28"/>
+      <c r="AH7" s="28"/>
+      <c r="AI7" s="28"/>
+      <c r="AJ7" s="28"/>
+      <c r="AK7" s="28"/>
+      <c r="AL7" s="26"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="41"/>
+      <c r="AO7" s="41"/>
+      <c r="AP7" s="41"/>
+      <c r="AQ7" s="41"/>
+      <c r="AR7" s="41"/>
+      <c r="AS7" s="23"/>
+      <c r="AT7" s="23"/>
+      <c r="AU7" s="23"/>
+      <c r="AV7" s="23"/>
+      <c r="AW7" s="23"/>
+      <c r="AX7" s="24"/>
     </row>
     <row r="8" spans="2:51" x14ac:dyDescent="0.2">
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="35"/>
-      <c r="V8" s="35"/>
-      <c r="W8" s="35"/>
-      <c r="X8" s="35"/>
-      <c r="Y8" s="35"/>
-      <c r="Z8" s="31"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="35"/>
-      <c r="AC8" s="35"/>
-      <c r="AD8" s="35"/>
-      <c r="AE8" s="35"/>
-      <c r="AF8" s="35"/>
-      <c r="AG8" s="35"/>
-      <c r="AH8" s="35"/>
-      <c r="AI8" s="35"/>
-      <c r="AJ8" s="35"/>
-      <c r="AK8" s="35"/>
-      <c r="AL8" s="31"/>
-      <c r="AM8" s="38"/>
-      <c r="AN8" s="38"/>
-      <c r="AO8" s="38"/>
-      <c r="AP8" s="38"/>
-      <c r="AQ8" s="38"/>
-      <c r="AR8" s="38"/>
-      <c r="AS8" s="54"/>
-      <c r="AT8" s="54"/>
-      <c r="AU8" s="54"/>
-      <c r="AV8" s="54"/>
-      <c r="AW8" s="54"/>
-      <c r="AX8" s="55"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="21"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="25"/>
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="25"/>
+      <c r="AJ8" s="25"/>
+      <c r="AK8" s="25"/>
+      <c r="AL8" s="21"/>
+      <c r="AM8" s="28"/>
+      <c r="AN8" s="28"/>
+      <c r="AO8" s="28"/>
+      <c r="AP8" s="28"/>
+      <c r="AQ8" s="28"/>
+      <c r="AR8" s="28"/>
+      <c r="AS8" s="44"/>
+      <c r="AT8" s="44"/>
+      <c r="AU8" s="44"/>
+      <c r="AV8" s="44"/>
+      <c r="AW8" s="44"/>
+      <c r="AX8" s="45"/>
       <c r="AY8" s="18"/>
     </row>
     <row r="9" spans="2:51" x14ac:dyDescent="0.2">
-      <c r="B9" s="52"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="35"/>
-      <c r="V9" s="35"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="35"/>
-      <c r="AC9" s="35"/>
-      <c r="AD9" s="35"/>
-      <c r="AE9" s="35"/>
-      <c r="AF9" s="35"/>
-      <c r="AG9" s="35"/>
-      <c r="AH9" s="35"/>
-      <c r="AI9" s="35"/>
-      <c r="AJ9" s="35"/>
-      <c r="AK9" s="35"/>
-      <c r="AL9" s="35"/>
-      <c r="AM9" s="53"/>
-      <c r="AN9" s="53"/>
-      <c r="AO9" s="53"/>
-      <c r="AP9" s="53"/>
-      <c r="AQ9" s="35"/>
-      <c r="AR9" s="35"/>
-      <c r="AS9" s="35"/>
-      <c r="AT9" s="53"/>
-      <c r="AU9" s="53"/>
-      <c r="AV9" s="53"/>
-      <c r="AW9" s="53"/>
-      <c r="AX9" s="35"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="25"/>
+      <c r="AH9" s="25"/>
+      <c r="AI9" s="25"/>
+      <c r="AJ9" s="25"/>
+      <c r="AK9" s="25"/>
+      <c r="AL9" s="25"/>
+      <c r="AM9" s="43"/>
+      <c r="AN9" s="43"/>
+      <c r="AO9" s="43"/>
+      <c r="AP9" s="43"/>
+      <c r="AQ9" s="25"/>
+      <c r="AR9" s="25"/>
+      <c r="AS9" s="25"/>
+      <c r="AT9" s="43"/>
+      <c r="AU9" s="43"/>
+      <c r="AV9" s="43"/>
+      <c r="AW9" s="43"/>
+      <c r="AX9" s="25"/>
       <c r="AY9" s="18"/>
     </row>
     <row r="10" spans="2:51" x14ac:dyDescent="0.2">
-      <c r="B10" s="52"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="35"/>
-      <c r="AD10" s="35"/>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="35"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="35"/>
-      <c r="AJ10" s="35"/>
-      <c r="AK10" s="35"/>
-      <c r="AL10" s="35"/>
-      <c r="AM10" s="35"/>
-      <c r="AN10" s="35"/>
-      <c r="AO10" s="35"/>
-      <c r="AP10" s="35"/>
-      <c r="AQ10" s="35"/>
-      <c r="AR10" s="35"/>
-      <c r="AS10" s="35"/>
-      <c r="AT10" s="35"/>
-      <c r="AU10" s="35"/>
-      <c r="AV10" s="35"/>
-      <c r="AW10" s="35"/>
-      <c r="AX10" s="38"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="25"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="25"/>
+      <c r="AI10" s="25"/>
+      <c r="AJ10" s="25"/>
+      <c r="AK10" s="25"/>
+      <c r="AL10" s="25"/>
+      <c r="AM10" s="25"/>
+      <c r="AN10" s="25"/>
+      <c r="AO10" s="25"/>
+      <c r="AP10" s="25"/>
+      <c r="AQ10" s="25"/>
+      <c r="AR10" s="25"/>
+      <c r="AS10" s="25"/>
+      <c r="AT10" s="25"/>
+      <c r="AU10" s="25"/>
+      <c r="AV10" s="25"/>
+      <c r="AW10" s="25"/>
+      <c r="AX10" s="28"/>
       <c r="AY10" s="18"/>
     </row>
     <row r="11" spans="2:51" x14ac:dyDescent="0.2">
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="35"/>
-      <c r="W11" s="35"/>
-      <c r="X11" s="35"/>
-      <c r="Y11" s="35"/>
-      <c r="Z11" s="35"/>
-      <c r="AA11" s="35"/>
-      <c r="AB11" s="35"/>
-      <c r="AC11" s="35"/>
-      <c r="AD11" s="35"/>
-      <c r="AE11" s="35"/>
-      <c r="AF11" s="35"/>
-      <c r="AG11" s="35"/>
-      <c r="AH11" s="35"/>
-      <c r="AI11" s="35"/>
-      <c r="AJ11" s="35"/>
-      <c r="AK11" s="35"/>
-      <c r="AL11" s="35"/>
-      <c r="AM11" s="35"/>
-      <c r="AN11" s="35"/>
-      <c r="AO11" s="35"/>
-      <c r="AP11" s="35"/>
-      <c r="AQ11" s="35"/>
-      <c r="AR11" s="35"/>
-      <c r="AS11" s="35"/>
-      <c r="AT11" s="35"/>
-      <c r="AU11" s="35"/>
-      <c r="AV11" s="35"/>
-      <c r="AW11" s="35"/>
-      <c r="AX11" s="35"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="25"/>
+      <c r="AI11" s="25"/>
+      <c r="AJ11" s="25"/>
+      <c r="AK11" s="25"/>
+      <c r="AL11" s="25"/>
+      <c r="AM11" s="25"/>
+      <c r="AN11" s="25"/>
+      <c r="AO11" s="25"/>
+      <c r="AP11" s="25"/>
+      <c r="AQ11" s="25"/>
+      <c r="AR11" s="25"/>
+      <c r="AS11" s="25"/>
+      <c r="AT11" s="25"/>
+      <c r="AU11" s="25"/>
+      <c r="AV11" s="25"/>
+      <c r="AW11" s="25"/>
+      <c r="AX11" s="25"/>
       <c r="AY11" s="18"/>
     </row>
     <row r="12" spans="2:51" x14ac:dyDescent="0.2">
@@ -1521,6 +1521,7 @@
     <mergeCell ref="AM2:AX2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1548,54 +1549,54 @@
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27" t="s">
+      <c r="C2" s="54"/>
+      <c r="D2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27" t="s">
+      <c r="E2" s="54"/>
+      <c r="F2" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27" t="s">
+      <c r="G2" s="54"/>
+      <c r="H2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27" t="s">
+      <c r="I2" s="54"/>
+      <c r="J2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27" t="s">
+      <c r="K2" s="54"/>
+      <c r="L2" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27" t="s">
+      <c r="M2" s="54"/>
+      <c r="N2" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27" t="s">
+      <c r="O2" s="54"/>
+      <c r="P2" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27" t="s">
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="28"/>
-      <c r="T2" s="27" t="s">
+      <c r="S2" s="58"/>
+      <c r="T2" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27" t="s">
+      <c r="U2" s="54"/>
+      <c r="V2" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27" t="s">
+      <c r="W2" s="54"/>
+      <c r="X2" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="Y2" s="27"/>
+      <c r="Y2" s="54"/>
       <c r="Z2" s="14"/>
       <c r="AA2" s="14"/>
     </row>
@@ -1607,51 +1608,51 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
-      <c r="R3" s="21" t="s">
+      <c r="R3" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="S3" s="22"/>
+      <c r="S3" s="61"/>
       <c r="T3" s="13"/>
       <c r="U3" s="13"/>
       <c r="V3" s="13"/>
       <c r="W3" s="8"/>
-      <c r="X3" s="21" t="s">
+      <c r="X3" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="Y3" s="21"/>
+      <c r="Y3" s="55"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
@@ -1885,11 +1886,11 @@
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
       <c r="S12" s="15"/>
-      <c r="T12" s="23" t="s">
+      <c r="T12" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
+      <c r="U12" s="63"/>
+      <c r="V12" s="63"/>
       <c r="W12" s="8"/>
       <c r="X12" s="8"/>
       <c r="Y12" s="8"/>
@@ -1900,34 +1901,34 @@
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="20"/>
+      <c r="E13" s="60"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
-      <c r="N13" s="20" t="s">
+      <c r="N13" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="O13" s="20"/>
+      <c r="O13" s="60"/>
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
       <c r="S13" s="15"/>
-      <c r="T13" s="19" t="s">
+      <c r="T13" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="20"/>
+      <c r="U13" s="60"/>
+      <c r="V13" s="60"/>
+      <c r="W13" s="60"/>
       <c r="X13" s="8"/>
       <c r="Y13" s="8"/>
     </row>
@@ -1938,11 +1939,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="T13:W13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="B4:E4"/>
     <mergeCell ref="X3:Y3"/>
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="F3:M3"/>
@@ -1953,13 +1956,11 @@
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="L2:M2"/>
-    <mergeCell ref="T13:W13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T12:V12"/>
-    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToWidth="4" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
